--- a/Day17.xlsx
+++ b/Day17.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utkarsh/Downloads/Accio_excel/Excel-for-DA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2593B0BE-7887-CA4E-AE34-B61C76DDE1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8564DBA7-7B96-D34F-9497-25D6986CA93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{AEE6927D-5555-D34D-B128-AF7E1450F2A3}"/>
   </bookViews>
@@ -36,9 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>POWER QUERY</t>
+  </si>
+  <si>
+    <t>1) You keep copy pasting</t>
   </si>
 </sst>
 </file>
@@ -413,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E09C4A7-ED9D-394E-890E-19DB02B0F6E9}">
-  <dimension ref="B3:C4"/>
+  <dimension ref="B3:C7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
@@ -426,6 +429,11 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
     </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B3:C4"/>
